--- a/exports/trend_1d/VEDL_full_report.xlsx
+++ b/exports/trend_1d/VEDL_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q77"/>
+  <dimension ref="A1:U77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>11.97</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42073</v>
+        <v>42074</v>
       </c>
       <c r="H2" t="n">
-        <v>84.8</v>
+        <v>82.45</v>
       </c>
       <c r="I2" t="n">
         <v>83.49748333709357</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K2" t="n">
-        <v>4.76</v>
+        <v>1.85</v>
       </c>
       <c r="L2" t="n">
         <v>1.85</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>16.43</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42124</v>
+        <v>42128</v>
       </c>
       <c r="H3" t="n">
-        <v>90.7</v>
+        <v>91.95</v>
       </c>
       <c r="I3" t="n">
         <v>91.89898984399198</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="K3" t="n">
-        <v>-10.01</v>
+        <v>-11.52</v>
       </c>
       <c r="L3" t="n">
         <v>14.19</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42089</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,22 +695,22 @@
         <v>12.18</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42149</v>
+        <v>42150</v>
       </c>
       <c r="H4" t="n">
-        <v>85.65000000000001</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="I4" t="n">
         <v>84.22296875417335</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K4" t="n">
-        <v>-6.85</v>
+        <v>-9.08</v>
       </c>
       <c r="L4" t="n">
-        <v>7.23</v>
+        <v>9.52</v>
       </c>
       <c r="M4" t="n">
         <v>0.89</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42152</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>16.41</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42285</v>
+        <v>42286</v>
       </c>
       <c r="H5" t="n">
-        <v>34.25</v>
+        <v>39.4</v>
       </c>
       <c r="I5" t="n">
         <v>37.47172153005921</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="K5" t="n">
-        <v>59.03</v>
+        <v>52.87</v>
       </c>
       <c r="L5" t="n">
         <v>5.14</v>
@@ -726,7 +785,7 @@
         <v>6.59</v>
       </c>
       <c r="N5" t="n">
-        <v>8.99</v>
+        <v>15.04</v>
       </c>
       <c r="O5" t="n">
         <v>-2.39</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>95</v>
+        <v>96</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42152</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>6</v>
+      </c>
+      <c r="U5" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -762,22 +833,22 @@
         <v>26.21</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42313</v>
+        <v>42314</v>
       </c>
       <c r="H6" t="n">
-        <v>34.8</v>
+        <v>33.9</v>
       </c>
       <c r="I6" t="n">
         <v>34.25892090371534</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K6" t="n">
-        <v>-11.68</v>
+        <v>-13.96</v>
       </c>
       <c r="L6" t="n">
-        <v>12.18</v>
+        <v>15.61</v>
       </c>
       <c r="M6" t="n">
         <v>2.43</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42306</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>23.66</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42430</v>
+        <v>42431</v>
       </c>
       <c r="H7" t="n">
-        <v>25.55</v>
+        <v>27.1</v>
       </c>
       <c r="I7" t="n">
         <v>26.19930076661092</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K7" t="n">
-        <v>24.63</v>
+        <v>20.06</v>
       </c>
       <c r="L7" t="n">
         <v>5.9</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42334</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>5</v>
+      </c>
+      <c r="U7" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>25.62</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42508</v>
+        <v>42509</v>
       </c>
       <c r="H8" t="n">
-        <v>37.3</v>
+        <v>35.2</v>
       </c>
       <c r="I8" t="n">
         <v>35.80363983375403</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K8" t="n">
-        <v>37.64</v>
+        <v>29.89</v>
       </c>
       <c r="L8" t="n">
         <v>2.77</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42460</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>21.76</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42520</v>
+        <v>42521</v>
       </c>
       <c r="H9" t="n">
-        <v>40.85</v>
+        <v>41.8</v>
       </c>
       <c r="I9" t="n">
         <v>41.6749529684528</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K9" t="n">
-        <v>-16.05</v>
+        <v>-18.75</v>
       </c>
       <c r="L9" t="n">
-        <v>17.19</v>
+        <v>20.31</v>
       </c>
       <c r="M9" t="n">
         <v>2.91</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42516</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>17.26</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42692</v>
+        <v>42695</v>
       </c>
       <c r="H10" t="n">
-        <v>87.55</v>
+        <v>84.34999999999999</v>
       </c>
       <c r="I10" t="n">
         <v>85.2122934809517</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="K10" t="n">
-        <v>109.45</v>
+        <v>101.79</v>
       </c>
       <c r="L10" t="n">
         <v>5.98</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>116</v>
+        <v>117</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42551</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>6</v>
+      </c>
+      <c r="U10" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>22.55</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42711</v>
+        <v>42712</v>
       </c>
       <c r="H11" t="n">
-        <v>101.15</v>
+        <v>106.7</v>
       </c>
       <c r="I11" t="n">
         <v>103.3680668224328</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K11" t="n">
-        <v>-19.92</v>
+        <v>-26.5</v>
       </c>
       <c r="L11" t="n">
-        <v>21.04</v>
+        <v>27.56</v>
       </c>
       <c r="M11" t="n">
         <v>2.43</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42698</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,28 +1247,28 @@
         <v>13.7</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42725</v>
+        <v>42726</v>
       </c>
       <c r="H12" t="n">
-        <v>98.55</v>
+        <v>94</v>
       </c>
       <c r="I12" t="n">
         <v>96.51843750823758</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K12" t="n">
-        <v>-7.64</v>
+        <v>-11.9</v>
       </c>
       <c r="L12" t="n">
-        <v>9.65</v>
+        <v>12.65</v>
       </c>
       <c r="M12" t="n">
         <v>1.45</v>
       </c>
       <c r="N12" t="n">
-        <v>3.04</v>
+        <v>4.62</v>
       </c>
       <c r="O12" t="n">
         <v>5.49</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42733</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>13.78</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42745</v>
+        <v>42746</v>
       </c>
       <c r="H13" t="n">
-        <v>101.7</v>
+        <v>104.1</v>
       </c>
       <c r="I13" t="n">
         <v>102.8074063343084</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K13" t="n">
-        <v>-8.19</v>
+        <v>-10.74</v>
       </c>
       <c r="L13" t="n">
-        <v>9.630000000000001</v>
+        <v>11.17</v>
       </c>
       <c r="M13" t="n">
         <v>1.12</v>
@@ -1191,7 +1346,19 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42733</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,28 +1385,28 @@
         <v>10.41</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42835</v>
+        <v>42836</v>
       </c>
       <c r="H14" t="n">
-        <v>120.9</v>
+        <v>111.4</v>
       </c>
       <c r="I14" t="n">
         <v>112.5305975355359</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K14" t="n">
-        <v>16.14</v>
+        <v>7.01</v>
       </c>
       <c r="L14" t="n">
         <v>1.59</v>
       </c>
       <c r="M14" t="n">
-        <v>1.3</v>
+        <v>6.33</v>
       </c>
       <c r="N14" t="n">
-        <v>3.83</v>
+        <v>7.86</v>
       </c>
       <c r="O14" t="n">
         <v>2.36</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>4</v>
+      </c>
+      <c r="U14" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>10.85</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42914</v>
+        <v>42915</v>
       </c>
       <c r="H15" t="n">
-        <v>106.5</v>
+        <v>110.65</v>
       </c>
       <c r="I15" t="n">
         <v>109.8134990555032</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K15" t="n">
-        <v>4.4</v>
+        <v>0.67</v>
       </c>
       <c r="L15" t="n">
         <v>4.26</v>
@@ -1305,7 +1484,19 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42852</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>10.59</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>43000</v>
+        <v>43003</v>
       </c>
       <c r="H16" t="n">
-        <v>138.05</v>
+        <v>137.5</v>
       </c>
       <c r="I16" t="n">
         <v>138.0223902542712</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="K16" t="n">
-        <v>24.76</v>
+        <v>24.27</v>
       </c>
       <c r="L16" t="n">
         <v>2.89</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>42943</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -1389,28 +1592,28 @@
         <v>9.42</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>43021</v>
+        <v>43024</v>
       </c>
       <c r="H17" t="n">
-        <v>144.55</v>
+        <v>151.25</v>
       </c>
       <c r="I17" t="n">
         <v>150.4472649368664</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K17" t="n">
-        <v>-5.13</v>
+        <v>-10</v>
       </c>
       <c r="L17" t="n">
-        <v>7.64</v>
+        <v>10.25</v>
       </c>
       <c r="M17" t="n">
         <v>1.36</v>
       </c>
       <c r="N17" t="n">
-        <v>4.04</v>
+        <v>4.64</v>
       </c>
       <c r="O17" t="n">
         <v>-0.4</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,22 +1661,22 @@
         <v>10.38</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43049</v>
+        <v>43052</v>
       </c>
       <c r="H18" t="n">
-        <v>145.75</v>
+        <v>141.35</v>
       </c>
       <c r="I18" t="n">
         <v>142.6060711016296</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K18" t="n">
-        <v>-3.64</v>
+        <v>-6.55</v>
       </c>
       <c r="L18" t="n">
-        <v>5.49</v>
+        <v>7.11</v>
       </c>
       <c r="M18" t="n">
         <v>0.9</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>43034</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>11.83</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43084</v>
+        <v>43087</v>
       </c>
       <c r="H19" t="n">
-        <v>133.25</v>
+        <v>138.3</v>
       </c>
       <c r="I19" t="n">
         <v>137.3666550129805</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K19" t="n">
-        <v>5.73</v>
+        <v>2.16</v>
       </c>
       <c r="L19" t="n">
         <v>3.43</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43069</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>14.73</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43137</v>
+        <v>43138</v>
       </c>
       <c r="H20" t="n">
-        <v>144.7</v>
+        <v>141.8</v>
       </c>
       <c r="I20" t="n">
         <v>141.9445826904635</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K20" t="n">
-        <v>4.63</v>
+        <v>2.53</v>
       </c>
       <c r="L20" t="n">
         <v>7.66</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43097</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>16.33</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43320</v>
+        <v>43321</v>
       </c>
       <c r="H21" t="n">
-        <v>97.95</v>
+        <v>100.75</v>
       </c>
       <c r="I21" t="n">
         <v>99.30238717782852</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K21" t="n">
-        <v>30.92</v>
+        <v>28.95</v>
       </c>
       <c r="L21" t="n">
         <v>9.98</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>126</v>
+        <v>127</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>7</v>
+      </c>
+      <c r="U21" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="22">
@@ -1674,28 +1937,28 @@
         <v>12.82</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43378</v>
+        <v>43381</v>
       </c>
       <c r="H22" t="n">
-        <v>101.25</v>
+        <v>89.2</v>
       </c>
       <c r="I22" t="n">
         <v>93.82975975367452</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="K22" t="n">
-        <v>0.5</v>
+        <v>-11.46</v>
       </c>
       <c r="L22" t="n">
-        <v>12.11</v>
+        <v>15.53</v>
       </c>
       <c r="M22" t="n">
         <v>3.7</v>
       </c>
       <c r="N22" t="n">
-        <v>3.79</v>
+        <v>11.9</v>
       </c>
       <c r="O22" t="n">
         <v>2.86</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43342</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>24.33</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43518</v>
+        <v>43521</v>
       </c>
       <c r="H23" t="n">
-        <v>71.3</v>
+        <v>72.05</v>
       </c>
       <c r="I23" t="n">
         <v>71.36139637024495</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="K23" t="n">
-        <v>20.07</v>
+        <v>19.23</v>
       </c>
       <c r="L23" t="n">
         <v>11.66</v>
@@ -1761,7 +2036,19 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>95</v>
+        <v>96</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43398</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>5</v>
+      </c>
+      <c r="U23" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>14.25</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43579</v>
+        <v>43580</v>
       </c>
       <c r="H24" t="n">
-        <v>73.75</v>
+        <v>71.7</v>
       </c>
       <c r="I24" t="n">
         <v>73.20913160147049</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K24" t="n">
-        <v>2.36</v>
+        <v>-0.49</v>
       </c>
       <c r="L24" t="n">
         <v>5</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43524</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>12.79</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43636</v>
+        <v>43637</v>
       </c>
       <c r="H25" t="n">
-        <v>72.45</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="I25" t="n">
         <v>72.45768964997212</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.05</v>
+        <v>-1.26</v>
       </c>
       <c r="L25" t="n">
         <v>3.21</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,22 +2213,22 @@
         <v>10.49</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43655</v>
+        <v>43656</v>
       </c>
       <c r="H26" t="n">
-        <v>67.34999999999999</v>
+        <v>66.65000000000001</v>
       </c>
       <c r="I26" t="n">
         <v>67.24259811072724</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K26" t="n">
-        <v>-7.23</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="L26" t="n">
-        <v>8.199999999999999</v>
+        <v>10.4</v>
       </c>
       <c r="M26" t="n">
         <v>0.84</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43643</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>10.92</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43727</v>
+        <v>43728</v>
       </c>
       <c r="H27" t="n">
-        <v>59.95</v>
+        <v>66.15000000000001</v>
       </c>
       <c r="I27" t="n">
         <v>62.99919200308214</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K27" t="n">
-        <v>10.05</v>
+        <v>0.75</v>
       </c>
       <c r="L27" t="n">
         <v>11.48</v>
@@ -1980,7 +2303,7 @@
         <v>3.13</v>
       </c>
       <c r="N27" t="n">
-        <v>7.83</v>
+        <v>10.34</v>
       </c>
       <c r="O27" t="n">
         <v>-1.04</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43671</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>19.63</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43787</v>
+        <v>43788</v>
       </c>
       <c r="H28" t="n">
-        <v>58.6</v>
+        <v>57.8</v>
       </c>
       <c r="I28" t="n">
         <v>57.99611327039279</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K28" t="n">
-        <v>-11.41</v>
+        <v>-12.62</v>
       </c>
       <c r="L28" t="n">
         <v>13.53</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43734</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>13.77</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43816</v>
+        <v>43817</v>
       </c>
       <c r="H29" t="n">
-        <v>62.95</v>
+        <v>63.15</v>
       </c>
       <c r="I29" t="n">
         <v>63.13221030327421</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K29" t="n">
-        <v>-8.91</v>
+        <v>-9.26</v>
       </c>
       <c r="L29" t="n">
         <v>10.47</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43797</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>11.78</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>43854</v>
+        <v>43857</v>
       </c>
       <c r="H30" t="n">
-        <v>64.65000000000001</v>
+        <v>61.25</v>
       </c>
       <c r="I30" t="n">
         <v>61.59227385450665</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="K30" t="n">
-        <v>2.38</v>
+        <v>-3.01</v>
       </c>
       <c r="L30" t="n">
         <v>7.28</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43825</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>12.55</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>43936</v>
+        <v>43937</v>
       </c>
       <c r="H31" t="n">
-        <v>27.35</v>
+        <v>29.3</v>
       </c>
       <c r="I31" t="n">
         <v>28.92480452688678</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K31" t="n">
-        <v>55.35</v>
+        <v>52.16</v>
       </c>
       <c r="L31" t="n">
         <v>3.59</v>
@@ -2217,7 +2588,19 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>4</v>
+      </c>
+      <c r="U31" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>34.32</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>44110</v>
+        <v>44111</v>
       </c>
       <c r="H32" t="n">
-        <v>55.95</v>
+        <v>48.95</v>
       </c>
       <c r="I32" t="n">
         <v>50.31208646682665</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="K32" t="n">
-        <v>90.95999999999999</v>
+        <v>67.06</v>
       </c>
       <c r="L32" t="n">
         <v>15.36</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>121</v>
+        <v>122</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>43951</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>7</v>
+      </c>
+      <c r="U32" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>22.13</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>44148</v>
+        <v>44149</v>
       </c>
       <c r="H33" t="n">
-        <v>41.3</v>
+        <v>41.55</v>
       </c>
       <c r="I33" t="n">
         <v>41.4904712267973</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K33" t="n">
-        <v>15.63</v>
+        <v>15.12</v>
       </c>
       <c r="L33" t="n">
         <v>15.22</v>
@@ -2331,7 +2726,19 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>44133</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>14.49</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>44183</v>
+        <v>44186</v>
       </c>
       <c r="H34" t="n">
-        <v>60.55</v>
+        <v>53.9</v>
       </c>
       <c r="I34" t="n">
         <v>54.1261118650086</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="K34" t="n">
-        <v>45.73</v>
+        <v>29.72</v>
       </c>
       <c r="L34" t="n">
         <v>2.29</v>
@@ -2379,7 +2786,7 @@
         <v>0.75</v>
       </c>
       <c r="N34" t="n">
-        <v>1.77</v>
+        <v>10.98</v>
       </c>
       <c r="O34" t="n">
         <v>0.61</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>44161</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -2415,28 +2834,28 @@
         <v>22.09</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>44188</v>
+        <v>44189</v>
       </c>
       <c r="H35" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="I35" t="n">
         <v>64.45239300536785</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K35" t="n">
-        <v>-15.03</v>
+        <v>-26.16</v>
       </c>
       <c r="L35" t="n">
-        <v>15.77</v>
+        <v>33.21</v>
       </c>
       <c r="M35" t="n">
-        <v>0.83</v>
+        <v>3.95</v>
       </c>
       <c r="N35" t="n">
-        <v>9.640000000000001</v>
+        <v>9.68</v>
       </c>
       <c r="O35" t="n">
         <v>-10.98</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>44196</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2472,28 +2903,28 @@
         <v>18.65</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44295</v>
+        <v>44298</v>
       </c>
       <c r="H36" t="n">
-        <v>101.1</v>
+        <v>92.34999999999999</v>
       </c>
       <c r="I36" t="n">
         <v>97.69516625383071</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="K36" t="n">
-        <v>48.68</v>
+        <v>35.81</v>
       </c>
       <c r="L36" t="n">
         <v>5.51</v>
       </c>
       <c r="M36" t="n">
-        <v>1.84</v>
+        <v>2.62</v>
       </c>
       <c r="N36" t="n">
-        <v>4.51</v>
+        <v>8.65</v>
       </c>
       <c r="O36" t="n">
         <v>9.68</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>44196</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>5</v>
+      </c>
+      <c r="U36" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="37">
@@ -2529,22 +2972,22 @@
         <v>14.54</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44312</v>
+        <v>44313</v>
       </c>
       <c r="H37" t="n">
-        <v>103.65</v>
+        <v>106.9</v>
       </c>
       <c r="I37" t="n">
         <v>104.7489488009574</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K37" t="n">
-        <v>-12.24</v>
+        <v>-15.76</v>
       </c>
       <c r="L37" t="n">
-        <v>13.81</v>
+        <v>16.4</v>
       </c>
       <c r="M37" t="n">
         <v>1.58</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44315</v>
+      </c>
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>11.84</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44364</v>
+        <v>44365</v>
       </c>
       <c r="H38" t="n">
-        <v>115.5</v>
+        <v>110.9</v>
       </c>
       <c r="I38" t="n">
         <v>114.3483504830196</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K38" t="n">
-        <v>8.039999999999999</v>
+        <v>3.74</v>
       </c>
       <c r="L38" t="n">
         <v>1.96</v>
@@ -2607,7 +3062,7 @@
         <v>2.06</v>
       </c>
       <c r="N38" t="n">
-        <v>3.74</v>
+        <v>3.98</v>
       </c>
       <c r="O38" t="n">
         <v>3.14</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44315</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>3</v>
+      </c>
+      <c r="U38" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -2643,28 +3110,28 @@
         <v>12.28</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44405</v>
+        <v>44406</v>
       </c>
       <c r="H39" t="n">
-        <v>119.8</v>
+        <v>128.75</v>
       </c>
       <c r="I39" t="n">
         <v>124.2756512248014</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K39" t="n">
-        <v>-8.029999999999999</v>
+        <v>-16.1</v>
       </c>
       <c r="L39" t="n">
-        <v>10.69</v>
+        <v>17.09</v>
       </c>
       <c r="M39" t="n">
         <v>2.17</v>
       </c>
       <c r="N39" t="n">
-        <v>4.93</v>
+        <v>7.47</v>
       </c>
       <c r="O39" t="n">
         <v>-3.98</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44371</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,25 +3179,25 @@
         <v>13.77</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44426</v>
+        <v>44428</v>
       </c>
       <c r="H40" t="n">
-        <v>132.25</v>
+        <v>119.4</v>
       </c>
       <c r="I40" t="n">
         <v>132.1420149992633</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K40" t="n">
-        <v>2.72</v>
+        <v>-7.26</v>
       </c>
       <c r="L40" t="n">
-        <v>6.76</v>
+        <v>8.23</v>
       </c>
       <c r="M40" t="n">
-        <v>1.51</v>
+        <v>2.5</v>
       </c>
       <c r="N40" t="n">
         <v>10.6</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44434</v>
+      </c>
+      <c r="S40" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2757,22 +3248,22 @@
         <v>23.92</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44481</v>
+        <v>44482</v>
       </c>
       <c r="H41" t="n">
-        <v>140.15</v>
+        <v>143.6</v>
       </c>
       <c r="I41" t="n">
         <v>141.1814372057576</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K41" t="n">
-        <v>-17.38</v>
+        <v>-20.27</v>
       </c>
       <c r="L41" t="n">
-        <v>19.39</v>
+        <v>21.69</v>
       </c>
       <c r="M41" t="n">
         <v>2.76</v>
@@ -2787,7 +3278,19 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44434</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>3</v>
+      </c>
+      <c r="U41" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>11.24</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44490</v>
+        <v>44491</v>
       </c>
       <c r="H42" t="n">
-        <v>158.6</v>
+        <v>145.75</v>
       </c>
       <c r="I42" t="n">
         <v>146.514230970827</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K42" t="n">
-        <v>10.45</v>
+        <v>1.5</v>
       </c>
       <c r="L42" t="n">
         <v>2.4</v>
@@ -2835,7 +3338,7 @@
         <v>2.08</v>
       </c>
       <c r="N42" t="n">
-        <v>4.24</v>
+        <v>8.1</v>
       </c>
       <c r="O42" t="n">
         <v>2.46</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44497</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,22 +3386,22 @@
         <v>22.02</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44524</v>
+        <v>44525</v>
       </c>
       <c r="H43" t="n">
-        <v>156.25</v>
+        <v>166.9</v>
       </c>
       <c r="I43" t="n">
         <v>161.5722917332704</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K43" t="n">
-        <v>-7.2</v>
+        <v>-14.51</v>
       </c>
       <c r="L43" t="n">
-        <v>12.32</v>
+        <v>16.36</v>
       </c>
       <c r="M43" t="n">
         <v>5.37</v>
@@ -2901,7 +3416,19 @@
         <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44497</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,22 +3455,22 @@
         <v>19.83</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44582</v>
+        <v>44585</v>
       </c>
       <c r="H44" t="n">
-        <v>145.5</v>
+        <v>140.1</v>
       </c>
       <c r="I44" t="n">
         <v>143.7241985526627</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="K44" t="n">
-        <v>-12.82</v>
+        <v>-16.06</v>
       </c>
       <c r="L44" t="n">
-        <v>15.04</v>
+        <v>16.63</v>
       </c>
       <c r="M44" t="n">
         <v>3.52</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,22 +3524,22 @@
         <v>13.2</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44595</v>
+        <v>44596</v>
       </c>
       <c r="H45" t="n">
-        <v>156.1</v>
+        <v>161.45</v>
       </c>
       <c r="I45" t="n">
         <v>156.3619819607645</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K45" t="n">
-        <v>-11.42</v>
+        <v>-15.24</v>
       </c>
       <c r="L45" t="n">
-        <v>13.67</v>
+        <v>17.45</v>
       </c>
       <c r="M45" t="n">
         <v>0.88</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,25 +3593,25 @@
         <v>13.44</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44615</v>
+        <v>44616</v>
       </c>
       <c r="H46" t="n">
-        <v>159.45</v>
+        <v>152.6</v>
       </c>
       <c r="I46" t="n">
         <v>153.1607109993487</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K46" t="n">
-        <v>-1.24</v>
+        <v>-5.48</v>
       </c>
       <c r="L46" t="n">
-        <v>5.08</v>
+        <v>6.19</v>
       </c>
       <c r="M46" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="N46" t="n">
         <v>4.65</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S46" t="b">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -3099,22 +3662,22 @@
         <v>14.28</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>44620</v>
+        <v>44622</v>
       </c>
       <c r="H47" t="n">
-        <v>173</v>
+        <v>176.4</v>
       </c>
       <c r="I47" t="n">
         <v>174.3901690620052</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K47" t="n">
-        <v>-13.37</v>
+        <v>-15.6</v>
       </c>
       <c r="L47" t="n">
-        <v>13.73</v>
+        <v>18.35</v>
       </c>
       <c r="M47" t="n">
         <v>2.49</v>
@@ -3129,7 +3692,19 @@
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S47" t="b">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>12.39</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>44683</v>
+        <v>44685</v>
       </c>
       <c r="H48" t="n">
-        <v>186.35</v>
+        <v>180.2</v>
       </c>
       <c r="I48" t="n">
         <v>180.6219896246203</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="K48" t="n">
-        <v>5.64</v>
+        <v>2.15</v>
       </c>
       <c r="L48" t="n">
         <v>9.18</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>3</v>
+      </c>
+      <c r="U48" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>12.74</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>44761</v>
+        <v>44762</v>
       </c>
       <c r="H49" t="n">
-        <v>104.7</v>
+        <v>111.65</v>
       </c>
       <c r="I49" t="n">
         <v>108.9244547915243</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K49" t="n">
-        <v>41.9</v>
+        <v>38.04</v>
       </c>
       <c r="L49" t="n">
         <v>4.5</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>3</v>
+      </c>
+      <c r="U49" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>15.7</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>44824</v>
+        <v>44825</v>
       </c>
       <c r="H50" t="n">
-        <v>124.65</v>
+        <v>123.55</v>
       </c>
       <c r="I50" t="n">
         <v>124.1544660902232</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K50" t="n">
-        <v>11.64</v>
+        <v>10.66</v>
       </c>
       <c r="L50" t="n">
         <v>7.48</v>
@@ -3300,7 +3899,19 @@
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>3</v>
+      </c>
+      <c r="U50" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="51">
@@ -3327,28 +3938,28 @@
         <v>14.78</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>44838</v>
+        <v>44840</v>
       </c>
       <c r="H51" t="n">
-        <v>124.2</v>
+        <v>130.55</v>
       </c>
       <c r="I51" t="n">
         <v>130.3769140648418</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K51" t="n">
-        <v>-0.53</v>
+        <v>-5.67</v>
       </c>
       <c r="L51" t="n">
-        <v>3.56</v>
+        <v>6.15</v>
       </c>
       <c r="M51" t="n">
         <v>4.33</v>
       </c>
       <c r="N51" t="n">
-        <v>4.41</v>
+        <v>5.11</v>
       </c>
       <c r="O51" t="n">
         <v>-0.88</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>14.04</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>44917</v>
+        <v>44918</v>
       </c>
       <c r="H52" t="n">
-        <v>135.25</v>
+        <v>127.1</v>
       </c>
       <c r="I52" t="n">
         <v>130.4364378276545</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K52" t="n">
-        <v>3.6</v>
+        <v>-2.64</v>
       </c>
       <c r="L52" t="n">
         <v>6.89</v>
@@ -3405,7 +4028,7 @@
         <v>5.06</v>
       </c>
       <c r="N52" t="n">
-        <v>5.11</v>
+        <v>6.03</v>
       </c>
       <c r="O52" t="n">
         <v>5.11</v>
@@ -3414,7 +4037,19 @@
         <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>3</v>
+      </c>
+      <c r="U52" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -3441,22 +4076,22 @@
         <v>13.52</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>44943</v>
+        <v>44944</v>
       </c>
       <c r="H53" t="n">
-        <v>142.9</v>
+        <v>145.9</v>
       </c>
       <c r="I53" t="n">
         <v>143.8223135332411</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K53" t="n">
-        <v>-12.43</v>
+        <v>-14.79</v>
       </c>
       <c r="L53" t="n">
-        <v>13.97</v>
+        <v>15.42</v>
       </c>
       <c r="M53" t="n">
         <v>1.1</v>
@@ -3471,7 +4106,19 @@
         <v>1</v>
       </c>
       <c r="Q53" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,22 +4145,22 @@
         <v>7.86</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>44960</v>
+        <v>44963</v>
       </c>
       <c r="H54" t="n">
-        <v>141.15</v>
+        <v>137.25</v>
       </c>
       <c r="I54" t="n">
         <v>139.6987856225507</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K54" t="n">
-        <v>-3.26</v>
+        <v>-5.93</v>
       </c>
       <c r="L54" t="n">
-        <v>5.35</v>
+        <v>6.34</v>
       </c>
       <c r="M54" t="n">
         <v>2.14</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>12.74</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45069</v>
+        <v>45070</v>
       </c>
       <c r="H55" t="n">
-        <v>128.65</v>
+        <v>130.05</v>
       </c>
       <c r="I55" t="n">
         <v>129.839687273246</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K55" t="n">
-        <v>6.27</v>
+        <v>5.25</v>
       </c>
       <c r="L55" t="n">
         <v>4.12</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>4</v>
+      </c>
+      <c r="U55" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="56">
@@ -3612,22 +4283,22 @@
         <v>7.78</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45076</v>
+        <v>45077</v>
       </c>
       <c r="H56" t="n">
-        <v>127.3</v>
+        <v>123.75</v>
       </c>
       <c r="I56" t="n">
         <v>125.7484345910853</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K56" t="n">
-        <v>-2.11</v>
+        <v>-4.84</v>
       </c>
       <c r="L56" t="n">
-        <v>3.08</v>
+        <v>5.04</v>
       </c>
       <c r="M56" t="n">
         <v>6.18</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,25 +4352,25 @@
         <v>8.880000000000001</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45198</v>
+        <v>45202</v>
       </c>
       <c r="H57" t="n">
-        <v>96.84999999999999</v>
+        <v>100.8</v>
       </c>
       <c r="I57" t="n">
         <v>99.48575141719455</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="K57" t="n">
-        <v>21.74</v>
+        <v>18.55</v>
       </c>
       <c r="L57" t="n">
         <v>3.15</v>
       </c>
       <c r="M57" t="n">
-        <v>1.91</v>
+        <v>3.72</v>
       </c>
       <c r="N57" t="n">
         <v>7.67</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>85</v>
+        <v>86</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>5</v>
+      </c>
+      <c r="U57" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="58">
@@ -3726,22 +4421,22 @@
         <v>11.16</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45224</v>
+        <v>45225</v>
       </c>
       <c r="H58" t="n">
-        <v>94.09999999999999</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="I58" t="n">
         <v>92.13869899884405</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K58" t="n">
-        <v>-6.65</v>
+        <v>-8.83</v>
       </c>
       <c r="L58" t="n">
-        <v>7.89</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="M58" t="n">
         <v>1.44</v>
@@ -3756,7 +4451,19 @@
         <v>1</v>
       </c>
       <c r="Q58" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S58" t="b">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -3783,25 +4490,25 @@
         <v>10.44</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45232</v>
+        <v>45233</v>
       </c>
       <c r="H59" t="n">
-        <v>100</v>
+        <v>101.8</v>
       </c>
       <c r="I59" t="n">
         <v>101.4917926281726</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K59" t="n">
-        <v>-8.81</v>
+        <v>-10.77</v>
       </c>
       <c r="L59" t="n">
-        <v>9.470000000000001</v>
+        <v>12.24</v>
       </c>
       <c r="M59" t="n">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="N59" t="n">
         <v>3.67</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S59" t="b">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>1</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>8.48</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45363</v>
+        <v>45364</v>
       </c>
       <c r="H60" t="n">
-        <v>125.2</v>
+        <v>116.35</v>
       </c>
       <c r="I60" t="n">
         <v>119.3251976279846</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="K60" t="n">
-        <v>22.99</v>
+        <v>14.29</v>
       </c>
       <c r="L60" t="n">
         <v>1.18</v>
@@ -3861,7 +4580,7 @@
         <v>1.87</v>
       </c>
       <c r="N60" t="n">
-        <v>4.98</v>
+        <v>7.07</v>
       </c>
       <c r="O60" t="n">
         <v>1.8</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>90</v>
+        <v>91</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>5</v>
+      </c>
+      <c r="U60" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="61">
@@ -3897,28 +4628,28 @@
         <v>15.77</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45379</v>
+        <v>45383</v>
       </c>
       <c r="H61" t="n">
-        <v>125.85</v>
+        <v>133.5</v>
       </c>
       <c r="I61" t="n">
         <v>133.0202053362793</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="K61" t="n">
-        <v>-8.17</v>
+        <v>-14.74</v>
       </c>
       <c r="L61" t="n">
-        <v>9.58</v>
+        <v>15.08</v>
       </c>
       <c r="M61" t="n">
         <v>1.29</v>
       </c>
       <c r="N61" t="n">
-        <v>3.39</v>
+        <v>6.08</v>
       </c>
       <c r="O61" t="n">
         <v>-7.07</v>
@@ -3927,7 +4658,19 @@
         <v>1</v>
       </c>
       <c r="Q61" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>12.05</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45446</v>
+        <v>45447</v>
       </c>
       <c r="H62" t="n">
-        <v>221.1</v>
+        <v>201.75</v>
       </c>
       <c r="I62" t="n">
         <v>203.5662334510247</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K62" t="n">
-        <v>65.62</v>
+        <v>51.12</v>
       </c>
       <c r="L62" t="n">
         <v>5.09</v>
@@ -3975,7 +4718,7 @@
         <v>1.46</v>
       </c>
       <c r="N62" t="n">
-        <v>3.63</v>
+        <v>8.75</v>
       </c>
       <c r="O62" t="n">
         <v>6.08</v>
@@ -3984,7 +4727,19 @@
         <v>1</v>
       </c>
       <c r="Q62" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>3</v>
+      </c>
+      <c r="U62" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>17.05</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45530</v>
+        <v>45531</v>
       </c>
       <c r="H63" t="n">
-        <v>223.6</v>
+        <v>224</v>
       </c>
       <c r="I63" t="n">
         <v>223.8975303919416</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K63" t="n">
-        <v>-10.83</v>
+        <v>-11.03</v>
       </c>
       <c r="L63" t="n">
         <v>14.8</v>
@@ -4041,7 +4796,19 @@
         <v>1</v>
       </c>
       <c r="Q63" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>3</v>
+      </c>
+      <c r="U63" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>8.26</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45581</v>
+        <v>45582</v>
       </c>
       <c r="H64" t="n">
-        <v>245.7</v>
+        <v>238.35</v>
       </c>
       <c r="I64" t="n">
         <v>238.6033028065122</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K64" t="n">
-        <v>9.69</v>
+        <v>6.41</v>
       </c>
       <c r="L64" t="n">
         <v>4.33</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>3</v>
+      </c>
+      <c r="U64" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -4125,28 +4904,28 @@
         <v>11.43</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45631</v>
+        <v>45632</v>
       </c>
       <c r="H65" t="n">
-        <v>238.5</v>
+        <v>253.1</v>
       </c>
       <c r="I65" t="n">
         <v>240.7857868997501</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K65" t="n">
-        <v>-0.06</v>
+        <v>-6.19</v>
       </c>
       <c r="L65" t="n">
-        <v>4.32</v>
+        <v>7.07</v>
       </c>
       <c r="M65" t="n">
         <v>2.51</v>
       </c>
       <c r="N65" t="n">
-        <v>3.24</v>
+        <v>6.12</v>
       </c>
       <c r="O65" t="n">
         <v>-2.99</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>3</v>
+      </c>
+      <c r="U65" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>10.06</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>45645</v>
+        <v>45646</v>
       </c>
       <c r="H66" t="n">
-        <v>248.5</v>
+        <v>240.9</v>
       </c>
       <c r="I66" t="n">
         <v>242.197095664445</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K66" t="n">
-        <v>-1.82</v>
+        <v>-4.82</v>
       </c>
       <c r="L66" t="n">
         <v>5.71</v>
@@ -4203,7 +4994,7 @@
         <v>2.91</v>
       </c>
       <c r="N66" t="n">
-        <v>2.01</v>
+        <v>3.06</v>
       </c>
       <c r="O66" t="n">
         <v>6.12</v>
@@ -4212,7 +5003,19 @@
         <v>1</v>
       </c>
       <c r="Q66" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S66" t="b">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>1</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -4239,19 +5042,19 @@
         <v>11.2</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>45721</v>
+        <v>45722</v>
       </c>
       <c r="H67" t="n">
-        <v>216.55</v>
+        <v>223.6</v>
       </c>
       <c r="I67" t="n">
         <v>222.5252201099456</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K67" t="n">
-        <v>10.11</v>
+        <v>7.18</v>
       </c>
       <c r="L67" t="n">
         <v>3.63</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>4</v>
+      </c>
+      <c r="U67" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="68">
@@ -4296,28 +5111,28 @@
         <v>12.32</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>45750</v>
+        <v>45751</v>
       </c>
       <c r="H68" t="n">
-        <v>221.85</v>
+        <v>202.65</v>
       </c>
       <c r="I68" t="n">
         <v>218.0616020135065</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K68" t="n">
-        <v>-0.78</v>
+        <v>-9.369999999999999</v>
       </c>
       <c r="L68" t="n">
-        <v>3.82</v>
+        <v>10.15</v>
       </c>
       <c r="M68" t="n">
         <v>2.04</v>
       </c>
       <c r="N68" t="n">
-        <v>3.98</v>
+        <v>8.65</v>
       </c>
       <c r="O68" t="n">
         <v>3.26</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>2</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -4353,28 +5180,28 @@
         <v>15.96</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>45786</v>
+        <v>45789</v>
       </c>
       <c r="H69" t="n">
-        <v>205.9</v>
+        <v>220.1</v>
       </c>
       <c r="I69" t="n">
         <v>215.1271505815319</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K69" t="n">
-        <v>-1.6</v>
+        <v>-8.609999999999999</v>
       </c>
       <c r="L69" t="n">
-        <v>8.83</v>
+        <v>9.18</v>
       </c>
       <c r="M69" t="n">
         <v>3.9</v>
       </c>
       <c r="N69" t="n">
-        <v>4.12</v>
+        <v>6.9</v>
       </c>
       <c r="O69" t="n">
         <v>-8.65</v>
@@ -4383,7 +5210,19 @@
         <v>1</v>
       </c>
       <c r="Q69" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>2</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -4410,19 +5249,19 @@
         <v>11.61</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>45867</v>
+        <v>45868</v>
       </c>
       <c r="H70" t="n">
-        <v>221.85</v>
+        <v>219.4</v>
       </c>
       <c r="I70" t="n">
         <v>220.0407183668375</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K70" t="n">
-        <v>0.8</v>
+        <v>-0.32</v>
       </c>
       <c r="L70" t="n">
         <v>4.16</v>
@@ -4440,7 +5279,19 @@
         <v>1</v>
       </c>
       <c r="Q70" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>3</v>
+      </c>
+      <c r="U70" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="71">
@@ -4467,22 +5318,22 @@
         <v>6.91</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>45902</v>
+        <v>45903</v>
       </c>
       <c r="H71" t="n">
-        <v>225.9</v>
+        <v>230</v>
       </c>
       <c r="I71" t="n">
         <v>229.4137932663461</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K71" t="n">
-        <v>-2.96</v>
+        <v>-4.83</v>
       </c>
       <c r="L71" t="n">
-        <v>4.17</v>
+        <v>5.38</v>
       </c>
       <c r="M71" t="n">
         <v>2.28</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>3</v>
+      </c>
+      <c r="U71" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="72">
@@ -4524,28 +5387,28 @@
         <v>7.26</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="H72" t="n">
-        <v>401.1</v>
+        <v>356.7</v>
       </c>
       <c r="I72" t="n">
         <v>360.6604794015584</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="K72" t="n">
-        <v>74.39</v>
+        <v>55.09</v>
       </c>
       <c r="L72" t="n">
         <v>1.7</v>
       </c>
       <c r="M72" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="N72" t="n">
-        <v>3.01</v>
+        <v>11.07</v>
       </c>
       <c r="O72" t="n">
         <v>1.81</v>
@@ -4554,7 +5417,19 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>101</v>
+        <v>102</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>6</v>
+      </c>
+      <c r="U72" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="73">
@@ -4581,19 +5456,19 @@
         <v>17.83</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="H73" t="n">
-        <v>377.6</v>
+        <v>385.75</v>
       </c>
       <c r="I73" t="n">
         <v>381.4561637907927</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K73" t="n">
-        <v>-5.86</v>
+        <v>-8.140000000000001</v>
       </c>
       <c r="L73" t="n">
         <v>10.78</v>
@@ -4611,7 +5486,19 @@
         <v>1</v>
       </c>
       <c r="Q73" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>3</v>
+      </c>
+      <c r="U73" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="74">
@@ -4638,28 +5525,28 @@
         <v>11.4</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="H74" t="n">
-        <v>404.9</v>
+        <v>271.55</v>
       </c>
       <c r="I74" t="n">
         <v>371.8596849395533</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K74" t="n">
-        <v>4.96</v>
+        <v>-29.6</v>
       </c>
       <c r="L74" t="n">
-        <v>3.99</v>
+        <v>30.34</v>
       </c>
       <c r="M74" t="n">
-        <v>1.36</v>
+        <v>28.5</v>
       </c>
       <c r="N74" t="n">
-        <v>2.83</v>
+        <v>32.93</v>
       </c>
       <c r="O74" t="n">
         <v>2.16</v>
@@ -4668,7 +5555,19 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S74" t="b">
+        <v>1</v>
+      </c>
+      <c r="T74" t="n">
+        <v>2</v>
+      </c>
+      <c r="U74" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -4695,19 +5594,19 @@
         <v>32.43</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="H75" t="n">
-        <v>275</v>
+        <v>278.85</v>
       </c>
       <c r="I75" t="n">
         <v>277.9342524319216</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K75" t="n">
-        <v>-1.27</v>
+        <v>-2.69</v>
       </c>
       <c r="L75" t="n">
         <v>32.57</v>
@@ -4725,7 +5624,19 @@
         <v>1</v>
       </c>
       <c r="Q75" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S75" t="b">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>4</v>
+      </c>
+      <c r="U75" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="76">
@@ -4752,22 +5663,22 @@
         <v>8.859999999999999</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>46276</v>
+        <v>46280</v>
       </c>
       <c r="H76" t="n">
-        <v>263.7</v>
+        <v>257</v>
       </c>
       <c r="I76" t="n">
         <v>261.1686035514608</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="K76" t="n">
-        <v>-5.43</v>
+        <v>-7.84</v>
       </c>
       <c r="L76" t="n">
-        <v>8.02</v>
+        <v>9.07</v>
       </c>
       <c r="M76" t="n">
         <v>1.88</v>
@@ -4782,7 +5693,19 @@
         <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S76" t="b">
+        <v>1</v>
+      </c>
+      <c r="T76" t="n">
+        <v>2</v>
+      </c>
+      <c r="U76" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="77">
@@ -4833,6 +5756,14 @@
       <c r="Q77" t="n">
         <v>30</v>
       </c>
+      <c r="R77" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S77" t="b">
+        <v>1</v>
+      </c>
+      <c r="T77" t="inlineStr"/>
+      <c r="U77" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9791,7 +10722,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>55.3</v>
+        <v>56.8</v>
       </c>
     </row>
     <row r="6">
@@ -9801,7 +10732,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7">
@@ -9811,7 +10742,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="8">
@@ -9821,7 +10752,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -9831,7 +10762,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10">
@@ -9841,7 +10772,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>119</v>
+        <v>121.8</v>
       </c>
     </row>
     <row r="11">
@@ -9881,7 +10812,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>8.34</v>
+        <v>3.02</v>
       </c>
     </row>
     <row r="15">
@@ -9891,7 +10822,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>13.84</v>
+        <v>6.96</v>
       </c>
     </row>
     <row r="16">
@@ -9901,7 +10832,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.69</v>
+        <v>-1.03</v>
       </c>
     </row>
     <row r="17">
@@ -9911,7 +10842,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>109.45</v>
+        <v>101.79</v>
       </c>
     </row>
     <row r="18">
@@ -9921,7 +10852,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>49.3</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -9931,7 +10862,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>8.220000000000001</v>
+        <v>9.949999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -9941,7 +10872,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>7.23</v>
+        <v>8.23</v>
       </c>
     </row>
     <row r="21">
@@ -9951,7 +10882,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>32.57</v>
+        <v>33.21</v>
       </c>
     </row>
     <row r="22">
@@ -9961,7 +10892,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
     </row>
     <row r="23">
@@ -9971,7 +10902,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="24">
@@ -9981,7 +10912,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3.06</v>
+        <v>3.59</v>
       </c>
     </row>
     <row r="25">
@@ -9991,7 +10922,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>11.7</v>
+        <v>28.5</v>
       </c>
     </row>
     <row r="26">
@@ -10001,7 +10932,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5.98</v>
+        <v>7.37</v>
       </c>
     </row>
     <row r="27">
@@ -10011,7 +10942,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>28.64</v>
+        <v>32.93</v>
       </c>
     </row>
     <row r="28">
@@ -10021,7 +10952,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>56</v>
+        <v>66</v>
       </c>
     </row>
     <row r="29">
